--- a/class.xlsx
+++ b/class.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>班级</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>跨境电子商务26302</t>
+  </si>
+  <si>
+    <t>跨境电子商务26303</t>
+  </si>
+  <si>
+    <t>跨境电子商务26301</t>
   </si>
 </sst>
 </file>
@@ -397,12 +403,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -529,7 +550,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -541,34 +562,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
@@ -653,8 +674,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -968,22 +992,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="24.5555555555556" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
